--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Enterprise Architect – Banking</t>
+          <t>Data, Analytics and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b71332e9c14c2344</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Data Enterprise Architect – Banking</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
+          <t>https://www.indeed.com/viewjob?jk=b71332e9c14c2344</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Senior Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>Full Circle Group &amp; The Leadership Circle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
+          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Agree Technologies and Solutions</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Agree Technologies and Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e05e42c5fd1053cf</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Business Analyst Sr</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>State of Ohio</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e9713b85aaa6a5</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
+          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2490,6 +2490,181 @@
         </is>
       </c>
       <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Moon Township, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
         </is>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>Compute - New</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Business Analyst Sr</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0150b99a3b3fea86</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8754e8d3551b49b0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
+          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2665,6 +2665,111 @@
         </is>
       </c>
       <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
         </is>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Compute - New</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdd485f349c9813e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Site Reliability Engineer (Azure)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19a6e4f42a1dcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior ELT Analytics Specialist (Database Administration Specialist 2, PN 20067096)</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State of Ohio</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868cad9be8cb3aa5</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8754e8d3551b49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
+          <t>https://www.indeed.com/viewjob?jk=8754e8d3551b49b0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Sr. Software Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=83326895ce89ffec</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,217 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise | HPE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Software Developer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Dublin, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Enterprise Architect – Banking</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b71332e9c14c2344</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Full Circle Group &amp; The Leadership Circle</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
+          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>Agree Technologies and Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agree Technologies and Solutions</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245f3c6627aa53a9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a7d79dfeae2865</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c810855cd475cddf</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (Cloud Engineer)</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, CodeBuild</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d6c6cf47d4b3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Azure)</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,182 +1441,182 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Data Domain Architect Senior Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af6f9746ce15f110</t>
+          <t>https://www.indeed.com/viewjob?jk=2251cb5230311649</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f7fca632ed3f48</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Unity Catalog, Cloud Storage, Spark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c75dd57a54105e4</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8754e8d3551b49b0</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Software Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83326895ce89ffec</t>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,322 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Galesburg, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Moon Township, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Southfield, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Beachwood, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Software Developer - Full Stack</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alkami Technology</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9c766989d27507</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1ce5d3e25c16d4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data, Analytics and AI Platform Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Alkami Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9c766989d27507</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Data, Analytics and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Senior Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>Full Circle Group &amp; The Leadership Circle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
+          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Agree Technologies and Solutions</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Agree Technologies and Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Domain Architect Senior Associate</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2251cb5230311649</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior ML Engineer, Generative AI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Domain Architect Senior Associate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=2251cb5230311649</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,29 +2341,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Data Solutions Advisor</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
+          <t>https://www.indeed.com/viewjob?jk=5d2c8ca96aa7a522</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2665,6 +2665,181 @@
         </is>
       </c>
       <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Moon Township, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
         </is>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data, Analytics and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alkami Technology</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Scala</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9c766989d27507</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data, Analytics and AI Platform Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Full Circle Group &amp; The Leadership Circle</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
+          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>Agree Technologies and Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agree Technologies and Solutions</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Senior Data Engineer (EDGE)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>AI Platform Engineer (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad0aa11b03bcee2</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ML Engineer, Generative AI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Data Domain Architect Senior Associate</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=2251cb5230311649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior ML Engineer, Generative AI</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Domain Architect Senior Associate</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2251cb5230311649</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
+          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Data Solutions Advisor</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=5d2c8ca96aa7a522</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Solutions Advisor</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d2c8ca96aa7a522</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, Power BI, Tableau, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fd5c7b34b56678</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,87 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Beachwood, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Data Enterprise Architect – Banking</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
+          <t>https://www.indeed.com/viewjob?jk=b71332e9c14c2344</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Senior Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>Full Circle Group &amp; The Leadership Circle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e308055f15971689</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (EDGE)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303a6ba70fa90d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Site Reliability Engineer (Azure)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
@@ -1413,52 +1413,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fffd4f5d1b3c90</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e593d6d7bcb6eda7</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Senior ML Engineer, Generative AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior ML Engineer, Generative AI</t>
+          <t>Data Domain Architect Senior Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
+          <t>https://www.indeed.com/viewjob?jk=2251cb5230311649</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Domain Architect Senior Associate</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2251cb5230311649</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
@@ -2148,25 +2148,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e644f982314c50c</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2025 - Summer 2026)</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4af8bf438b9426a</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Solutions Advisor</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, dbt</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d2c8ca96aa7a522</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8754e8d3551b49b0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+          <t>https://www.indeed.com/viewjob?jk=83326895ce89ffec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer Go Outdoors Payments</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Solutions Advisor</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=5d2c8ca96aa7a522</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Application Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,122 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Enterprise Architect – Banking</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b71332e9c14c2344</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Senior Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Full Circle Group &amp; The Leadership Circle</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
+          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>Agree Technologies and Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Agree Technologies and Solutions</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a0449408242d4cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Azure)</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, MySQL, NoSQL, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68867f5f2f53aa49</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,207 +1196,207 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7228093a638b5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfe41cb3e214682</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666c929b887d4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1492fbbf44262d</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
@@ -1523,160 +1523,160 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Computing Specialist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Pat N Sally Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=50abe9e2081e3326</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SCP Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2229a1b23116108</t>
+          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,312 +1791,312 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637189f4ee313108</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d36f4f63dca52da</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior ML Engineer, Generative AI</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Domain Architect Senior Associate</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2251cb5230311649</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Advertising &amp; Partnerships Ad Products Internships – Academic Year</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Moon Township, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, PySpark, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892cce569405d61</t>
+          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,540 +2341,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>AI DevOps / Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Hermeus</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8754e8d3551b49b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Minerva</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Sr. Software Architect</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Applied Information Sciences</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83326895ce89ffec</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Go Outdoors Payments</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Brandt Information Services, Inc.</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d19947dba07869ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Data Solutions Advisor</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d2c8ca96aa7a522</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Application Security Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Fort Collins, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84af24884d8c2311</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior Software Developer - Full Stack</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Galesburg, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Moon Township, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Southfield, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Beachwood, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
         </is>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1ce5d3e25c16d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a759ca089bff0f85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data, Analytics and AI Platform Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1ce5d3e25c16d4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
+          <t>https://www.indeed.com/viewjob?jk=6436f900bda01324</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=14776783056c9570</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=89e35139815f4a73</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data, Analytics and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Senior Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>Full Circle Group &amp; The Leadership Circle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
+          <t>https://www.indeed.com/viewjob?jk=29eb4b25500beb8f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Network Operations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agree Technologies and Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e57463bb555dc770</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Dev/ MLOps Engineer I (Full Stack)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
         </is>
       </c>
     </row>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Agree Technologies and Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,137 +1301,137 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1462,33 +1462,33 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,81 +1497,81 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Computing Specialist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pat N Sally Inc</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50abe9e2081e3326</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,207 +1651,207 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SCP Health</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Scala, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,89 +2001,89 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33261b56b6b771e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6955ba1be4a330</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Moon Township, PA, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709beae9964c38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ccfc0a42fa5999</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>SCP Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae19b83fb3c677f</t>
+          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a6c16c455fbe550</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,332 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19b9d1ca199648e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BI Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Health Care Service Corporation</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>UVA Health</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>University of Virginia</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Empower Pharmacy</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Software Developer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dublin, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI DevOps / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hermeus</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Minerva</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,69 +1361,69 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Sr. Java Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,42 +1616,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Scala, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Scala, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RRS Enterprises</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SCP Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>SCP Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Developer - Full Stack</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Developer - Full Stack</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,15 +2656,50 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Minerva</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Remote Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29eb4b25500beb8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e17f6626567905dd</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
+          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Data Engineer III - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agree Technologies and Solutions</t>
+          <t>Paradigm Corp</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lombard, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc31db62fba45fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
+          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,24 +1326,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Databricks, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c00d3722b6113c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Middle Office Production Support Officer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, Splunk, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=6d477484091d86d9</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - Real Estate Mortgage Servicing</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,42 +1616,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5353391b47b16722</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Scala, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Scala, NoSQL, ETL, ELT, Docker</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - AI Solutions Engineer - Associate - Dallas</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,104 +1991,104 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Databricks, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebff3fb9a8fa2</t>
+          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RRS Enterprises</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef3473575569109</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Service Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=675136ff532a1cc5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Experienced Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>SCP Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SCP Health</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,15 +2691,50 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Minerva</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Network Operations Engineer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57463bb555dc770</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dev/ MLOps Engineer I (Full Stack)</t>
+          <t>Associate Network Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427875b29ec1de14</t>
+          <t>https://www.indeed.com/viewjob?jk=e57463bb555dc770</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff3451d72aca5a0</t>
+          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d91e7d74c6a8abc</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT Data Engineer III - Remote</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paradigm Corp</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lombard, IL, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Spark, Scala, Kafka, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a983900d06af5f80</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Eagle Outfitters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ceff8454ebfac5</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9997a7eee60c24</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software AI Engineer Mid-Level, Context Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,172 +1231,172 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=851e43960c5deeba</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Middle Office Production Support Officer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, Splunk, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d477484091d86d9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Middle Office Production Support Officer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, Splunk, Docker</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d477484091d86d9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Java Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dec65bf183a746b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, RDS, Azure, Spark, Scala, NoSQL, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37dd105237e7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0a27f5cad734cd</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef54466fd6bf7b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9046bcfc59025</t>
+          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Scala, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,137 +1861,137 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Azure Integration Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Intent Design Pvt Ltd</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=753eee17cd52656e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Service Reliability Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
+          <t>https://www.indeed.com/viewjob?jk=675136ff532a1cc5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Service Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675136ff532a1cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Sr Software AI Engineer 3 - Context Engineering</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,164 +2176,164 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Experienced Business Intelligence Developer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Tableau, CI/CD, Jenkins, Maven</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832138786e2c4867</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Entry-level Software Engineer – Spring Boot Microservices and Core Java</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106aa03227443434</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SCP Health</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EMR, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e966d98ccd8eeb74</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,190 +2551,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Software Engineer – Full Stack</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Empower Pharmacy</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Software Developer - Full Stack</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abc88efd61aa5a80</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>AI DevOps / Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Hermeus</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Minerva</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, IAM, RDS, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=638d31785669a8b7</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software AI Engineer Mid-Level, Context Engineering</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Software AI Engineer Mid-Level, Context Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,104 +1186,104 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d043d29787d8ef9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>GCP Data Cloud Architect with AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, Spark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=707ff3ea38954494</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Middle Office Production Support Officer</t>
+          <t>Kong API Developer / API Gateway Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>LVTLABS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Hawthorn Wds, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, Splunk, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d477484091d86d9</t>
+          <t>https://www.indeed.com/viewjob?jk=26b193a0ca9b282b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, Databricks, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=0d640b390d938641</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=3abc772dea7afb0b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Spark, Scala, NoSQL, ETL, ELT, Docker</t>
+          <t>AWS, S3, IAM, Azure, Google Cloud Platform, Hive, Impala, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9f1a6d4065db66</t>
+          <t>https://www.indeed.com/viewjob?jk=fa27147966b86ffa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=1cab7004c6202bd5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intent Design Pvt Ltd</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753eee17cd52656e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>MedReview</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
+          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Service Reliability Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675136ff532a1cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Azure Integration Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Intent Design Pvt Ltd</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=753eee17cd52656e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Integration Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>intent design ltd</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=76fbbcfefd3014c8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Senior Service Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=675136ff532a1cc5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software AI Engineer 3 - Context Engineering</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior ML Engineer, Generative AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Sr Software AI Engineer 3 - Context Engineering</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,29 +2481,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,15 +2551,225 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BI Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Health Care Service Corporation</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UVA Health</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>University of Virginia</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI DevOps / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hermeus</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Empower Pharmacy</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Minerva</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>

--- a/results/job_matches_2026-04-21.xlsx
+++ b/results/job_matches_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,147 +468,147 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a759ca089bff0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=7a26555a7e1695a9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JCPenney</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1ce5d3e25c16d4</t>
+          <t>https://www.indeed.com/viewjob?jk=41d41dba6e5bbf64</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6436f900bda01324</t>
+          <t>https://www.indeed.com/viewjob?jk=a759ca089bff0f85</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JCPenney</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14776783056c9570</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1ce5d3e25c16d4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e35139815f4a73</t>
+          <t>https://www.indeed.com/viewjob?jk=6436f900bda01324</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data, Analytics and AI Platform Engineer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
+          <t>https://www.indeed.com/viewjob?jk=14776783056c9570</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEVELOPER L3</t>
+          <t>Data, Analytics and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Azure, Databricks, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
+          <t>https://www.indeed.com/viewjob?jk=d3dca5ca9c21a095</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Full Circle Group &amp; The Leadership Circle</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a78b57cc2e9cee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Remote Azure Cloud Engineer</t>
+          <t>Senior Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Full Circle Group &amp; The Leadership Circle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Snowflake, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17f6626567905dd</t>
+          <t>https://www.indeed.com/viewjob?jk=68e7d84738583957</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Developer</t>
+          <t>Remote Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WISE EQUATION SOLUTION INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e17f6626567905dd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Network Operations Engineer</t>
+          <t>AWS Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Glue, Redshift, S3, SQS, SNS, RDS, Databricks, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e57463bb555dc770</t>
+          <t>https://www.indeed.com/viewjob?jk=840498587d7ca5cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe2835081fe7ce2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Data Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
+          <t>https://www.indeed.com/viewjob?jk=11c49f85138a1b57</t>
         </is>
       </c>
     </row>
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; AI Platform Engineer</t>
+          <t>Senior AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brown and Caldwell</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7573a96b762a6443</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>Brown and Caldwell</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f7841a504710c6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>SmartThings</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,69 +1046,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
+          <t>https://www.indeed.com/viewjob?jk=f3621f9dee302478</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
+          <t>https://www.indeed.com/viewjob?jk=f264eea4efd38f74</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1d62ec0f497740</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software AI Engineer Mid-Level, Context Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software AI Engineer Mid-Level, Context Engineering</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4eea7c69bb40</t>
+          <t>https://www.indeed.com/viewjob?jk=13a4ffe330a49d68</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Data Cloud Architect with AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FreshDirect</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Data Modeling, Star Schema</t>
+          <t>ECS, RDS, Azure, Databricks, Spark, Scala, MLOps, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f37c9c95ba03e4</t>
+          <t>https://www.indeed.com/viewjob?jk=4d82e274d453e4ad</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Scala</t>
+          <t>AWS, Kinesis, Redshift, Azure, Hadoop, Hive, Spark, Kafka, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad28557fa5dd3f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9577f06fc17064b</t>
         </is>
       </c>
     </row>
@@ -1378,25 +1378,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kong API Developer / API Gateway Engineer</t>
+          <t>Azure Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LVTLABS</t>
+          <t>Witherite Law Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hawthorn Wds, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b193a0ca9b282b</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Witherite Law Group</t>
+          <t>The Shade Store</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f99f229d1e8a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Developer [US Based Employee]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Shade Store</t>
+          <t>Vegas Tickets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64251d971f917430</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer [US Based Employee]</t>
+          <t>Software Developer II - REMOTE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vegas Tickets</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c6576ad0babb42</t>
+          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
         </is>
       </c>
     </row>
@@ -1553,25 +1553,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Developer II - REMOTE</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08a27412cb3aca9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c99f9dffdd56b5b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Infrastructure Systems Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
+          <t>https://www.indeed.com/viewjob?jk=48f3f6761af5a6ca</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
+          <t>https://www.indeed.com/viewjob?jk=5d57d61e65bfc57f</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Reinsurance Data Engineer New</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kohlberg Kravis Roberts &amp; Co.</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, S3, Azure, Google Cloud Platform, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
+          <t>https://www.indeed.com/viewjob?jk=42f1ba78ee960a45</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Reinsurance Data Engineer New</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Kohlberg Kravis Roberts &amp; Co.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
+          <t>https://www.indeed.com/viewjob?jk=56a86f8f8ea85f81</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BI ETL Data Developer II or III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Miami University</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oxford, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, NoSQL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
+          <t>https://www.indeed.com/viewjob?jk=3f41f6be104426dc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>BI ETL Data Developer II or III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Miami University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oxford, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>Redshift, IAM, RDS, Azure, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68922ec4695e5f78</t>
+          <t>https://www.indeed.com/viewjob?jk=be7780cda1b04985</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Podimetrics, Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ETL Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MedReview</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Cloud Storage, Scala, Kafka, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e39c7d622d171</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0c90ddd19e5a5f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Podimetrics, Inc</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Kafka, Data Modeling, dbt, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c32862f1c73054</t>
+          <t>https://www.indeed.com/viewjob?jk=83f649135cd571c8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Application Automation - Summer Intern</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intent Design Pvt Ltd</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=753eee17cd52656e</t>
+          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Software Engineer I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>Symetra</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7a3e15c84ea264</t>
+          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>ICT Data Analyst/Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>intent design ltd</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76fbbcfefd3014c8</t>
+          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Service Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Franklin Templeton</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675136ff532a1cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ICT Data Analyst/Scientist</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=785c40fa6b6ef824</t>
+          <t>https://www.indeed.com/viewjob?jk=18b5f2a66adcafce</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Automation - Summer Intern</t>
+          <t>Sr. Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Jenkins</t>
+          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e747b081b28ed805</t>
+          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I</t>
+          <t>Sr Software AI Engineer 3 - Context Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Symetra</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5753698810124b20</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer + Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Franklin Templeton</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56905870be888df6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7aa5a7d64f9c11</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior ML Engineer, Generative AI</t>
+          <t>PowerBI Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Contingent Crew, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372304a6a2fe598d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
+          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, MongoDB, NoSQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13bf6308ab860db0</t>
+          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Software AI Engineer 3 - Context Engineering</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1bac54e3a5abdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PowerBI Developer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Contingent Crew, LLC</t>
+          <t>Health Care Service Corporation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6960d866243637</t>
+          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>UVA Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986441a4b7cccaf5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9835c179aace3eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06059acfed7a424</t>
+          <t>https://www.indeed.com/viewjob?jk=0f85aef5c7b6e68f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Health Care Service Corporation</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b830867236986c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>AI DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>UVA Health</t>
+          <t>Hermeus</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f1e012731e28218</t>
+          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34114659eae6a8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI DevOps / Platform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hermeus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,87 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623f9a35a70c68ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Software Engineer – Full Stack</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Empower Pharmacy</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e78a720e18a8f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Minerva</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Redshift, S3, IAM, RDS, Spark, Scala, Snowflake, MySQL, Data Modeling, dbt</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed82e0ddad246dda</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5e5cf7170d5ea7</t>
         </is>
       </c>
     </row>
